--- a/artfynd/A 63862-2021 artfynd.xlsx
+++ b/artfynd/A 63862-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63862-2021 artfynd.xlsx
+++ b/artfynd/A 63862-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20295</v>
+        <v>20294</v>
       </c>
       <c r="B2" t="n">
-        <v>57574</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>100117</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Bonaparte, 1840</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540765.396071077</v>
+        <v>540765</v>
       </c>
       <c r="R2" t="n">
-        <v>6245544.452585051</v>
+        <v>6245544</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2008-04-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-04-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>20293</v>
       </c>
       <c r="B3" t="n">
-        <v>57548</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540765.396071077</v>
+        <v>540765</v>
       </c>
       <c r="R3" t="n">
-        <v>6245544.452585051</v>
+        <v>6245544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2008-04-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-04-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -927,47 +897,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20294</v>
+        <v>20295</v>
       </c>
       <c r="B4" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100117</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540765.396071077</v>
+        <v>540765</v>
       </c>
       <c r="R4" t="n">
-        <v>6245544.452585051</v>
+        <v>6245544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +974,9 @@
           <t>2008-04-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-04-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 63862-2021 artfynd.xlsx
+++ b/artfynd/A 63862-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20293</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20295</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>